--- a/data_lake/macro/South Korea/Interest.xlsx
+++ b/data_lake/macro/South Korea/Interest.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCDC8A4-3442-4C46-B541-3EEBAF8C2F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119A86D7-342D-264D-83C9-7D0613C68B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12240" yWindow="780" windowWidth="23760" windowHeight="20800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KORP7DR" sheetId="1" r:id="rId1"/>
+    <sheet name="info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="19">
   <si>
     <t>Release Date</t>
   </si>
@@ -59,33 +60,74 @@
   <si>
     <t>Base Date</t>
   </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ticker</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monthly</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>South Korea</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KORP7DR</t>
+  </si>
+  <si>
+    <t>BOK</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/south-korean-interest-rate-decision-473</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -102,16 +144,30 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,17 +175,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -140,10 +212,10 @@
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -153,10 +225,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -435,18 +520,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H296"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.296875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="8" customWidth="1"/>
     <col min="4" max="4" width="10" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.8984375" style="10"/>
-    <col min="8" max="8" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.796875" style="6"/>
+    <col min="5" max="7" width="8.83203125" style="10"/>
+    <col min="8" max="8" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -470,7 +555,7 @@
       </c>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>36286</v>
       </c>
@@ -491,7 +576,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>36314</v>
       </c>
@@ -512,7 +597,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>36348</v>
       </c>
@@ -533,7 +618,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>36377</v>
       </c>
@@ -554,7 +639,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>36405</v>
       </c>
@@ -575,7 +660,7 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>36440</v>
       </c>
@@ -596,7 +681,7 @@
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>36468</v>
       </c>
@@ -617,7 +702,7 @@
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>36496</v>
       </c>
@@ -638,7 +723,7 @@
       </c>
       <c r="H9" s="5"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>36531</v>
       </c>
@@ -659,7 +744,7 @@
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>36566</v>
       </c>
@@ -680,7 +765,7 @@
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>36594</v>
       </c>
@@ -701,7 +786,7 @@
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>36622</v>
       </c>
@@ -722,7 +807,7 @@
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>36650</v>
       </c>
@@ -743,7 +828,7 @@
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>36685</v>
       </c>
@@ -764,7 +849,7 @@
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>36713</v>
       </c>
@@ -785,7 +870,7 @@
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>36741</v>
       </c>
@@ -806,7 +891,7 @@
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>36776</v>
       </c>
@@ -827,7 +912,7 @@
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>36804</v>
       </c>
@@ -848,7 +933,7 @@
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>36839</v>
       </c>
@@ -869,7 +954,7 @@
       </c>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>36867</v>
       </c>
@@ -890,7 +975,7 @@
       </c>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>36902</v>
       </c>
@@ -911,7 +996,7 @@
       </c>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>36930</v>
       </c>
@@ -932,7 +1017,7 @@
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>36958</v>
       </c>
@@ -953,7 +1038,7 @@
       </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>36987</v>
       </c>
@@ -974,7 +1059,7 @@
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>37019</v>
       </c>
@@ -995,7 +1080,7 @@
       </c>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>37049</v>
       </c>
@@ -1016,7 +1101,7 @@
       </c>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>37077</v>
       </c>
@@ -1037,7 +1122,7 @@
       </c>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>37112</v>
       </c>
@@ -1058,7 +1143,7 @@
       </c>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>37140</v>
       </c>
@@ -1079,7 +1164,7 @@
       </c>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>37153</v>
       </c>
@@ -1100,7 +1185,7 @@
       </c>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>37175</v>
       </c>
@@ -1121,7 +1206,7 @@
       </c>
       <c r="H32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>37203</v>
       </c>
@@ -1142,7 +1227,7 @@
       </c>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>37231</v>
       </c>
@@ -1163,7 +1248,7 @@
       </c>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>37266</v>
       </c>
@@ -1184,7 +1269,7 @@
       </c>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>37294</v>
       </c>
@@ -1205,7 +1290,7 @@
       </c>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>37322</v>
       </c>
@@ -1226,7 +1311,7 @@
       </c>
       <c r="H37" s="5"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>37350</v>
       </c>
@@ -1247,7 +1332,7 @@
       </c>
       <c r="H38" s="5"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>37383</v>
       </c>
@@ -1268,7 +1353,7 @@
       </c>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>37412</v>
       </c>
@@ -1289,7 +1374,7 @@
       </c>
       <c r="H40" s="5"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>37441</v>
       </c>
@@ -1310,7 +1395,7 @@
       </c>
       <c r="H41" s="5"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>37474</v>
       </c>
@@ -1331,7 +1416,7 @@
       </c>
       <c r="H42" s="5"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>37511</v>
       </c>
@@ -1352,7 +1437,7 @@
       </c>
       <c r="H43" s="5"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>37539</v>
       </c>
@@ -1373,7 +1458,7 @@
       </c>
       <c r="H44" s="5"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>37567</v>
       </c>
@@ -1394,7 +1479,7 @@
       </c>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>37602</v>
       </c>
@@ -1415,7 +1500,7 @@
       </c>
       <c r="H46" s="5"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>37630</v>
       </c>
@@ -1436,7 +1521,7 @@
       </c>
       <c r="H47" s="5"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>37658</v>
       </c>
@@ -1457,7 +1542,7 @@
       </c>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>37686</v>
       </c>
@@ -1478,7 +1563,7 @@
       </c>
       <c r="H49" s="5"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>37721</v>
       </c>
@@ -1499,7 +1584,7 @@
       </c>
       <c r="H50" s="5"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>37754</v>
       </c>
@@ -1520,7 +1605,7 @@
       </c>
       <c r="H51" s="5"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>37784</v>
       </c>
@@ -1541,7 +1626,7 @@
       </c>
       <c r="H52" s="5"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>37812</v>
       </c>
@@ -1562,7 +1647,7 @@
       </c>
       <c r="H53" s="5"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>37840</v>
       </c>
@@ -1583,7 +1668,7 @@
       </c>
       <c r="H54" s="5"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>37873</v>
       </c>
@@ -1604,7 +1689,7 @@
       </c>
       <c r="H55" s="5"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>37903</v>
       </c>
@@ -1625,7 +1710,7 @@
       </c>
       <c r="H56" s="5"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>37931</v>
       </c>
@@ -1646,7 +1731,7 @@
       </c>
       <c r="H57" s="5"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>37966</v>
       </c>
@@ -1667,7 +1752,7 @@
       </c>
       <c r="H58" s="5"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>37994</v>
       </c>
@@ -1688,7 +1773,7 @@
       </c>
       <c r="H59" s="5"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>38023</v>
       </c>
@@ -1709,7 +1794,7 @@
       </c>
       <c r="H60" s="5"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>38057</v>
       </c>
@@ -1730,7 +1815,7 @@
       </c>
       <c r="H61" s="5"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>38085</v>
       </c>
@@ -1751,7 +1836,7 @@
       </c>
       <c r="H62" s="5"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>38113</v>
       </c>
@@ -1772,7 +1857,7 @@
       </c>
       <c r="H63" s="5"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>38148</v>
       </c>
@@ -1793,7 +1878,7 @@
       </c>
       <c r="H64" s="5"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>38176</v>
       </c>
@@ -1814,7 +1899,7 @@
       </c>
       <c r="H65" s="5"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>38211</v>
       </c>
@@ -1835,7 +1920,7 @@
       </c>
       <c r="H66" s="5"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>38239</v>
       </c>
@@ -1856,7 +1941,7 @@
       </c>
       <c r="H67" s="5"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>38267</v>
       </c>
@@ -1877,7 +1962,7 @@
       </c>
       <c r="H68" s="5"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>38302</v>
       </c>
@@ -1898,7 +1983,7 @@
       </c>
       <c r="H69" s="5"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>38330</v>
       </c>
@@ -1919,7 +2004,7 @@
       </c>
       <c r="H70" s="5"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>38365</v>
       </c>
@@ -1940,7 +2025,7 @@
       </c>
       <c r="H71" s="5"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>38398</v>
       </c>
@@ -1961,7 +2046,7 @@
       </c>
       <c r="H72" s="5"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>38421</v>
       </c>
@@ -1982,7 +2067,7 @@
       </c>
       <c r="H73" s="5"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>38449</v>
       </c>
@@ -2003,7 +2088,7 @@
       </c>
       <c r="H74" s="5"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>38484</v>
       </c>
@@ -2024,7 +2109,7 @@
       </c>
       <c r="H75" s="5"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>38512</v>
       </c>
@@ -2045,7 +2130,7 @@
       </c>
       <c r="H76" s="5"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>38540</v>
       </c>
@@ -2066,7 +2151,7 @@
       </c>
       <c r="H77" s="5"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>38575</v>
       </c>
@@ -2087,7 +2172,7 @@
       </c>
       <c r="H78" s="5"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>38603</v>
       </c>
@@ -2108,7 +2193,7 @@
       </c>
       <c r="H79" s="5"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>38636</v>
       </c>
@@ -2129,7 +2214,7 @@
       </c>
       <c r="H80" s="5"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>38666</v>
       </c>
@@ -2150,7 +2235,7 @@
       </c>
       <c r="H81" s="5"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>38694</v>
       </c>
@@ -2171,7 +2256,7 @@
       </c>
       <c r="H82" s="5"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>38729</v>
       </c>
@@ -2192,7 +2277,7 @@
       </c>
       <c r="H83" s="5"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>38757</v>
       </c>
@@ -2213,7 +2298,7 @@
       </c>
       <c r="H84" s="5"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>38785</v>
       </c>
@@ -2234,7 +2319,7 @@
       </c>
       <c r="H85" s="5"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>38814</v>
       </c>
@@ -2255,7 +2340,7 @@
       </c>
       <c r="H86" s="5"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>38848</v>
       </c>
@@ -2276,7 +2361,7 @@
       </c>
       <c r="H87" s="5"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>38876</v>
       </c>
@@ -2297,7 +2382,7 @@
       </c>
       <c r="H88" s="5"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>38905</v>
       </c>
@@ -2318,7 +2403,7 @@
       </c>
       <c r="H89" s="5"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>38939</v>
       </c>
@@ -2339,7 +2424,7 @@
       </c>
       <c r="H90" s="5"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>38967</v>
       </c>
@@ -2360,7 +2445,7 @@
       </c>
       <c r="H91" s="5"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="7">
         <v>39002</v>
       </c>
@@ -2381,7 +2466,7 @@
       </c>
       <c r="H92" s="5"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <v>39030</v>
       </c>
@@ -2402,7 +2487,7 @@
       </c>
       <c r="H93" s="5"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>39058</v>
       </c>
@@ -2423,7 +2508,7 @@
       </c>
       <c r="H94" s="5"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <v>39093</v>
       </c>
@@ -2444,7 +2529,7 @@
       </c>
       <c r="H95" s="5"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <v>39121</v>
       </c>
@@ -2465,7 +2550,7 @@
       </c>
       <c r="H96" s="5"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <v>39149</v>
       </c>
@@ -2486,7 +2571,7 @@
       </c>
       <c r="H97" s="5"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <v>39184</v>
       </c>
@@ -2507,7 +2592,7 @@
       </c>
       <c r="H98" s="5"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <v>39212</v>
       </c>
@@ -2528,7 +2613,7 @@
       </c>
       <c r="H99" s="5"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <v>39241</v>
       </c>
@@ -2549,7 +2634,7 @@
       </c>
       <c r="H100" s="5"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <v>39275</v>
       </c>
@@ -2570,7 +2655,7 @@
       </c>
       <c r="H101" s="5"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <v>39303</v>
       </c>
@@ -2591,7 +2676,7 @@
       </c>
       <c r="H102" s="5"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <v>39332</v>
       </c>
@@ -2612,7 +2697,7 @@
       </c>
       <c r="H103" s="5"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <v>39366</v>
       </c>
@@ -2633,7 +2718,7 @@
       </c>
       <c r="H104" s="5"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <v>39394</v>
       </c>
@@ -2654,7 +2739,7 @@
       </c>
       <c r="H105" s="5"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <v>39423</v>
       </c>
@@ -2675,7 +2760,7 @@
       </c>
       <c r="H106" s="5"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <v>39457</v>
       </c>
@@ -2696,7 +2781,7 @@
       </c>
       <c r="H107" s="5"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <v>39491</v>
       </c>
@@ -2717,7 +2802,7 @@
       </c>
       <c r="H108" s="5"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <v>39514</v>
       </c>
@@ -2738,7 +2823,7 @@
       </c>
       <c r="H109" s="5"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>39548</v>
       </c>
@@ -2759,7 +2844,7 @@
       </c>
       <c r="H110" s="5"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <v>39576</v>
       </c>
@@ -2780,7 +2865,7 @@
       </c>
       <c r="H111" s="5"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <v>39611</v>
       </c>
@@ -2801,7 +2886,7 @@
       </c>
       <c r="H112" s="5"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
         <v>39639</v>
       </c>
@@ -2822,7 +2907,7 @@
       </c>
       <c r="H113" s="5"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="7">
         <v>39667</v>
       </c>
@@ -2843,7 +2928,7 @@
       </c>
       <c r="H114" s="5"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="7">
         <v>39702</v>
       </c>
@@ -2864,7 +2949,7 @@
       </c>
       <c r="H115" s="5"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="7">
         <v>39730</v>
       </c>
@@ -2885,7 +2970,7 @@
       </c>
       <c r="H116" s="5"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
         <v>39748</v>
       </c>
@@ -2906,7 +2991,7 @@
       </c>
       <c r="H117" s="5"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="7">
         <v>39759</v>
       </c>
@@ -2927,7 +3012,7 @@
       </c>
       <c r="H118" s="5"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
         <v>39793</v>
       </c>
@@ -2948,7 +3033,7 @@
       </c>
       <c r="H119" s="5"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
         <v>39822</v>
       </c>
@@ -2969,7 +3054,7 @@
       </c>
       <c r="H120" s="5"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <v>39856</v>
       </c>
@@ -2990,7 +3075,7 @@
       </c>
       <c r="H121" s="5"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <v>39884</v>
       </c>
@@ -3011,7 +3096,7 @@
       </c>
       <c r="H122" s="5"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <v>39912</v>
       </c>
@@ -3032,7 +3117,7 @@
       </c>
       <c r="H123" s="5"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <v>39945</v>
       </c>
@@ -3053,7 +3138,7 @@
       </c>
       <c r="H124" s="5"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <v>39975</v>
       </c>
@@ -3074,7 +3159,7 @@
       </c>
       <c r="H125" s="5"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <v>40003</v>
       </c>
@@ -3095,7 +3180,7 @@
       </c>
       <c r="H126" s="5"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <v>40036</v>
       </c>
@@ -3116,7 +3201,7 @@
       </c>
       <c r="H127" s="5"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <v>40066</v>
       </c>
@@ -3137,7 +3222,7 @@
       </c>
       <c r="H128" s="5"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <v>40095</v>
       </c>
@@ -3158,7 +3243,7 @@
       </c>
       <c r="H129" s="5"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <v>40129</v>
       </c>
@@ -3179,7 +3264,7 @@
       </c>
       <c r="H130" s="5"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <v>40157</v>
       </c>
@@ -3200,7 +3285,7 @@
       </c>
       <c r="H131" s="5"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <v>40186</v>
       </c>
@@ -3221,7 +3306,7 @@
       </c>
       <c r="H132" s="5"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <v>40220</v>
       </c>
@@ -3242,7 +3327,7 @@
       </c>
       <c r="H133" s="5"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <v>40248</v>
       </c>
@@ -3263,7 +3348,7 @@
       </c>
       <c r="H134" s="5"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <v>40277</v>
       </c>
@@ -3284,7 +3369,7 @@
       </c>
       <c r="H135" s="5"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <v>40310</v>
       </c>
@@ -3305,7 +3390,7 @@
       </c>
       <c r="H136" s="5"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <v>40339</v>
       </c>
@@ -3326,7 +3411,7 @@
       </c>
       <c r="H137" s="5"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>40368</v>
       </c>
@@ -3347,7 +3432,7 @@
       </c>
       <c r="H138" s="5"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>40402</v>
       </c>
@@ -3368,7 +3453,7 @@
       </c>
       <c r="H139" s="5"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="7">
         <v>40430</v>
       </c>
@@ -3389,7 +3474,7 @@
       </c>
       <c r="H140" s="5"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>40465</v>
       </c>
@@ -3410,7 +3495,7 @@
       </c>
       <c r="H141" s="5"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>40498</v>
       </c>
@@ -3431,7 +3516,7 @@
       </c>
       <c r="H142" s="5"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>40521</v>
       </c>
@@ -3452,7 +3537,7 @@
       </c>
       <c r="H143" s="5"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="7">
         <v>40556</v>
       </c>
@@ -3476,7 +3561,7 @@
       </c>
       <c r="H144" s="5"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <v>40585</v>
       </c>
@@ -3500,7 +3585,7 @@
       </c>
       <c r="H145" s="5"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <v>40612</v>
       </c>
@@ -3524,7 +3609,7 @@
       </c>
       <c r="H146" s="5"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <v>40645</v>
       </c>
@@ -3548,7 +3633,7 @@
       </c>
       <c r="H147" s="5"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <v>40676</v>
       </c>
@@ -3572,7 +3657,7 @@
       </c>
       <c r="H148" s="5"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <v>40704</v>
       </c>
@@ -3596,7 +3681,7 @@
       </c>
       <c r="H149" s="5"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <v>40738</v>
       </c>
@@ -3620,7 +3705,7 @@
       </c>
       <c r="H150" s="5"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <v>40766</v>
       </c>
@@ -3644,7 +3729,7 @@
       </c>
       <c r="H151" s="5"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <v>40794</v>
       </c>
@@ -3668,7 +3753,7 @@
       </c>
       <c r="H152" s="5"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <v>40829</v>
       </c>
@@ -3692,7 +3777,7 @@
       </c>
       <c r="H153" s="5"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <v>40858</v>
       </c>
@@ -3716,7 +3801,7 @@
       </c>
       <c r="H154" s="5"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <v>40885</v>
       </c>
@@ -3740,7 +3825,7 @@
       </c>
       <c r="H155" s="5"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <v>40921</v>
       </c>
@@ -3764,7 +3849,7 @@
       </c>
       <c r="H156" s="5"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <v>40948</v>
       </c>
@@ -3788,7 +3873,7 @@
       </c>
       <c r="H157" s="5"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <v>40976</v>
       </c>
@@ -3812,7 +3897,7 @@
       </c>
       <c r="H158" s="5"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="7">
         <v>41012</v>
       </c>
@@ -3836,7 +3921,7 @@
       </c>
       <c r="H159" s="5"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="7">
         <v>41039</v>
       </c>
@@ -3860,7 +3945,7 @@
       </c>
       <c r="H160" s="5"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="7">
         <v>41068</v>
       </c>
@@ -3884,7 +3969,7 @@
       </c>
       <c r="H161" s="5"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="7">
         <v>41102</v>
       </c>
@@ -3908,7 +3993,7 @@
       </c>
       <c r="H162" s="5"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="7">
         <v>41130</v>
       </c>
@@ -3932,7 +4017,7 @@
       </c>
       <c r="H163" s="5"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="7">
         <v>41165</v>
       </c>
@@ -3956,7 +4041,7 @@
       </c>
       <c r="H164" s="5"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="7">
         <v>41193</v>
       </c>
@@ -3980,7 +4065,7 @@
       </c>
       <c r="H165" s="5"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="7">
         <v>41222</v>
       </c>
@@ -4004,7 +4089,7 @@
       </c>
       <c r="H166" s="5"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <v>41256</v>
       </c>
@@ -4028,7 +4113,7 @@
       </c>
       <c r="H167" s="5"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <v>41285</v>
       </c>
@@ -4052,7 +4137,7 @@
       </c>
       <c r="H168" s="5"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <v>41319</v>
       </c>
@@ -4076,7 +4161,7 @@
       </c>
       <c r="H169" s="5"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <v>41347</v>
       </c>
@@ -4100,7 +4185,7 @@
       </c>
       <c r="H170" s="5"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <v>41375</v>
       </c>
@@ -4124,7 +4209,7 @@
       </c>
       <c r="H171" s="5"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <v>41403</v>
       </c>
@@ -4148,7 +4233,7 @@
       </c>
       <c r="H172" s="5"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <v>41438</v>
       </c>
@@ -4172,7 +4257,7 @@
       </c>
       <c r="H173" s="5"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <v>41466</v>
       </c>
@@ -4196,7 +4281,7 @@
       </c>
       <c r="H174" s="5"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <v>41494</v>
       </c>
@@ -4220,7 +4305,7 @@
       </c>
       <c r="H175" s="5"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <v>41529</v>
       </c>
@@ -4244,7 +4329,7 @@
       </c>
       <c r="H176" s="5"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <v>41557</v>
       </c>
@@ -4268,7 +4353,7 @@
       </c>
       <c r="H177" s="5"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <v>41592</v>
       </c>
@@ -4292,7 +4377,7 @@
       </c>
       <c r="H178" s="5"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <v>41620</v>
       </c>
@@ -4316,7 +4401,7 @@
       </c>
       <c r="H179" s="5"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <v>41648</v>
       </c>
@@ -4340,7 +4425,7 @@
       </c>
       <c r="H180" s="5"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <v>41683</v>
       </c>
@@ -4364,7 +4449,7 @@
       </c>
       <c r="H181" s="5"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <v>41711</v>
       </c>
@@ -4388,7 +4473,7 @@
       </c>
       <c r="H182" s="5"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <v>41739</v>
       </c>
@@ -4412,7 +4497,7 @@
       </c>
       <c r="H183" s="5"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <v>41768</v>
       </c>
@@ -4436,7 +4521,7 @@
       </c>
       <c r="H184" s="5"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="7">
         <v>41802</v>
       </c>
@@ -4460,7 +4545,7 @@
       </c>
       <c r="H185" s="5"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="7">
         <v>41830</v>
       </c>
@@ -4484,7 +4569,7 @@
       </c>
       <c r="H186" s="5"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="7">
         <v>41865</v>
       </c>
@@ -4508,7 +4593,7 @@
       </c>
       <c r="H187" s="5"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="7">
         <v>41894</v>
       </c>
@@ -4532,7 +4617,7 @@
       </c>
       <c r="H188" s="5"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="7">
         <v>41927</v>
       </c>
@@ -4556,7 +4641,7 @@
       </c>
       <c r="H189" s="5"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="7">
         <v>41956</v>
       </c>
@@ -4580,7 +4665,7 @@
       </c>
       <c r="H190" s="5"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="7">
         <v>41984</v>
       </c>
@@ -4604,7 +4689,7 @@
       </c>
       <c r="H191" s="5"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="7">
         <v>42019</v>
       </c>
@@ -4628,7 +4713,7 @@
       </c>
       <c r="H192" s="5"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="7">
         <v>42052</v>
       </c>
@@ -4652,7 +4737,7 @@
       </c>
       <c r="H193" s="5"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="7">
         <v>42075</v>
       </c>
@@ -4676,7 +4761,7 @@
       </c>
       <c r="H194" s="5"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="7">
         <v>42103</v>
       </c>
@@ -4700,7 +4785,7 @@
       </c>
       <c r="H195" s="5"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="7">
         <v>42139</v>
       </c>
@@ -4724,7 +4809,7 @@
       </c>
       <c r="H196" s="5"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="7">
         <v>42166</v>
       </c>
@@ -4748,7 +4833,7 @@
       </c>
       <c r="H197" s="5"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="7">
         <v>42194</v>
       </c>
@@ -4772,7 +4857,7 @@
       </c>
       <c r="H198" s="5"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="7">
         <v>42229</v>
       </c>
@@ -4796,7 +4881,7 @@
       </c>
       <c r="H199" s="5"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="7">
         <v>42258</v>
       </c>
@@ -4820,7 +4905,7 @@
       </c>
       <c r="H200" s="5"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="7">
         <v>42292</v>
       </c>
@@ -4844,7 +4929,7 @@
       </c>
       <c r="H201" s="5"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="7">
         <v>42320</v>
       </c>
@@ -4868,7 +4953,7 @@
       </c>
       <c r="H202" s="5"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="7">
         <v>42348</v>
       </c>
@@ -4892,7 +4977,7 @@
       </c>
       <c r="H203" s="5"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="7">
         <v>42383</v>
       </c>
@@ -4916,7 +5001,7 @@
       </c>
       <c r="H204" s="5"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <v>42416</v>
       </c>
@@ -4940,7 +5025,7 @@
       </c>
       <c r="H205" s="5"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <v>42439</v>
       </c>
@@ -4964,7 +5049,7 @@
       </c>
       <c r="H206" s="5"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <v>42479</v>
       </c>
@@ -4988,7 +5073,7 @@
       </c>
       <c r="H207" s="5"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <v>42503</v>
       </c>
@@ -5012,7 +5097,7 @@
       </c>
       <c r="H208" s="5"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="7">
         <v>42530</v>
       </c>
@@ -5036,7 +5121,7 @@
       </c>
       <c r="H209" s="5"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="7">
         <v>42565</v>
       </c>
@@ -5060,7 +5145,7 @@
       </c>
       <c r="H210" s="5"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="7">
         <v>42593</v>
       </c>
@@ -5084,7 +5169,7 @@
       </c>
       <c r="H211" s="5"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="7">
         <v>42622</v>
       </c>
@@ -5108,7 +5193,7 @@
       </c>
       <c r="H212" s="5"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="7">
         <v>42656</v>
       </c>
@@ -5132,7 +5217,7 @@
       </c>
       <c r="H213" s="5"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="7">
         <v>42685</v>
       </c>
@@ -5156,7 +5241,7 @@
       </c>
       <c r="H214" s="5"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="7">
         <v>42719</v>
       </c>
@@ -5180,7 +5265,7 @@
       </c>
       <c r="H215" s="5"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="7">
         <v>42748</v>
       </c>
@@ -5204,7 +5289,7 @@
       </c>
       <c r="H216" s="5"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="7">
         <v>42789</v>
       </c>
@@ -5228,7 +5313,7 @@
       </c>
       <c r="H217" s="5"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="7">
         <v>42838</v>
       </c>
@@ -5252,7 +5337,7 @@
       </c>
       <c r="H218" s="5"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="7">
         <v>42880</v>
       </c>
@@ -5276,7 +5361,7 @@
       </c>
       <c r="H219" s="5"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="7">
         <v>42929</v>
       </c>
@@ -5300,7 +5385,7 @@
       </c>
       <c r="H220" s="5"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="7">
         <v>42978</v>
       </c>
@@ -5324,7 +5409,7 @@
       </c>
       <c r="H221" s="5"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="7">
         <v>43027</v>
       </c>
@@ -5348,7 +5433,7 @@
       </c>
       <c r="H222" s="5"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="7">
         <v>43069</v>
       </c>
@@ -5372,7 +5457,7 @@
       </c>
       <c r="H223" s="5"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="7">
         <v>43118</v>
       </c>
@@ -5396,7 +5481,7 @@
       </c>
       <c r="H224" s="5"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="7">
         <v>43158</v>
       </c>
@@ -5420,7 +5505,7 @@
       </c>
       <c r="H225" s="5"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="7">
         <v>43202</v>
       </c>
@@ -5444,7 +5529,7 @@
       </c>
       <c r="H226" s="5"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="7">
         <v>43244</v>
       </c>
@@ -5468,7 +5553,7 @@
       </c>
       <c r="H227" s="5"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="7">
         <v>43293</v>
       </c>
@@ -5492,7 +5577,7 @@
       </c>
       <c r="H228" s="5"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="7">
         <v>43343</v>
       </c>
@@ -5516,7 +5601,7 @@
       </c>
       <c r="H229" s="5"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="7">
         <v>43391</v>
       </c>
@@ -5540,7 +5625,7 @@
       </c>
       <c r="H230" s="5"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="7">
         <v>43434</v>
       </c>
@@ -5564,7 +5649,7 @@
       </c>
       <c r="H231" s="5"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="7">
         <v>43489</v>
       </c>
@@ -5588,7 +5673,7 @@
       </c>
       <c r="H232" s="5"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="7">
         <v>43524</v>
       </c>
@@ -5612,7 +5697,7 @@
       </c>
       <c r="H233" s="5"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="7">
         <v>43573</v>
       </c>
@@ -5636,7 +5721,7 @@
       </c>
       <c r="H234" s="5"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="7">
         <v>43616</v>
       </c>
@@ -5660,7 +5745,7 @@
       </c>
       <c r="H235" s="5"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="7">
         <v>43664</v>
       </c>
@@ -5684,7 +5769,7 @@
       </c>
       <c r="H236" s="5"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="7">
         <v>43707</v>
       </c>
@@ -5708,7 +5793,7 @@
       </c>
       <c r="H237" s="5"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="7">
         <v>43754</v>
       </c>
@@ -5732,7 +5817,7 @@
       </c>
       <c r="H238" s="5"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="7">
         <v>43798</v>
       </c>
@@ -5756,7 +5841,7 @@
       </c>
       <c r="H239" s="5"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="7">
         <v>43847</v>
       </c>
@@ -5780,7 +5865,7 @@
       </c>
       <c r="H240" s="5"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="7">
         <v>43888</v>
       </c>
@@ -5804,7 +5889,7 @@
       </c>
       <c r="H241" s="5"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="7">
         <v>43906</v>
       </c>
@@ -5825,7 +5910,7 @@
       </c>
       <c r="H242" s="5"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="7">
         <v>43930</v>
       </c>
@@ -5849,7 +5934,7 @@
       </c>
       <c r="H243" s="5"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="7">
         <v>43979</v>
       </c>
@@ -5873,7 +5958,7 @@
       </c>
       <c r="H244" s="5"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="7">
         <v>44028</v>
       </c>
@@ -5897,7 +5982,7 @@
       </c>
       <c r="H245" s="5"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="7">
         <v>44070</v>
       </c>
@@ -5921,7 +6006,7 @@
       </c>
       <c r="H246" s="5"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="7">
         <v>44118</v>
       </c>
@@ -5945,7 +6030,7 @@
       </c>
       <c r="H247" s="5"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="7">
         <v>44161</v>
       </c>
@@ -5969,7 +6054,7 @@
       </c>
       <c r="H248" s="5"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="7">
         <v>44211</v>
       </c>
@@ -5993,7 +6078,7 @@
       </c>
       <c r="H249" s="5"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="7">
         <v>44252</v>
       </c>
@@ -6017,7 +6102,7 @@
       </c>
       <c r="H250" s="5"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="7">
         <v>44301</v>
       </c>
@@ -6041,7 +6126,7 @@
       </c>
       <c r="H251" s="5"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="7">
         <v>44343</v>
       </c>
@@ -6065,7 +6150,7 @@
       </c>
       <c r="H252" s="5"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="7">
         <v>44392</v>
       </c>
@@ -6089,7 +6174,7 @@
       </c>
       <c r="H253" s="5"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="7">
         <v>44434</v>
       </c>
@@ -6113,7 +6198,7 @@
       </c>
       <c r="H254" s="5"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="7">
         <v>44481</v>
       </c>
@@ -6137,7 +6222,7 @@
       </c>
       <c r="H255" s="5"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="7">
         <v>44525</v>
       </c>
@@ -6161,7 +6246,7 @@
       </c>
       <c r="H256" s="5"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="7">
         <v>44575</v>
       </c>
@@ -6185,7 +6270,7 @@
       </c>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="7">
         <v>44616</v>
       </c>
@@ -6209,7 +6294,7 @@
       </c>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="7">
         <v>44665</v>
       </c>
@@ -6233,7 +6318,7 @@
       </c>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="7">
         <v>44707</v>
       </c>
@@ -6257,7 +6342,7 @@
       </c>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="7">
         <v>44755</v>
       </c>
@@ -6281,7 +6366,7 @@
       </c>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="7">
         <v>44798</v>
       </c>
@@ -6305,7 +6390,7 @@
       </c>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="7">
         <v>44846</v>
       </c>
@@ -6329,7 +6414,7 @@
       </c>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="7">
         <v>44889</v>
       </c>
@@ -6353,7 +6438,7 @@
       </c>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="7">
         <v>44939</v>
       </c>
@@ -6377,7 +6462,7 @@
       </c>
       <c r="H265" s="5"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="7">
         <v>44980</v>
       </c>
@@ -6401,7 +6486,7 @@
       </c>
       <c r="H266" s="5"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="7">
         <v>45027</v>
       </c>
@@ -6425,7 +6510,7 @@
       </c>
       <c r="H267" s="5"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="7">
         <v>45071</v>
       </c>
@@ -6449,7 +6534,7 @@
       </c>
       <c r="H268" s="5"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="7">
         <v>45120</v>
       </c>
@@ -6473,7 +6558,7 @@
       </c>
       <c r="H269" s="5"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="7">
         <v>45162</v>
       </c>
@@ -6497,7 +6582,7 @@
       </c>
       <c r="H270" s="5"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="7">
         <v>45218</v>
       </c>
@@ -6521,7 +6606,7 @@
       </c>
       <c r="H271" s="5"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="7">
         <v>45260</v>
       </c>
@@ -6545,7 +6630,7 @@
       </c>
       <c r="H272" s="5"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="7">
         <v>45302</v>
       </c>
@@ -6569,7 +6654,7 @@
       </c>
       <c r="H273" s="5"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="7">
         <v>45344</v>
       </c>
@@ -6593,7 +6678,7 @@
       </c>
       <c r="H274" s="5"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="7">
         <v>45394</v>
       </c>
@@ -6617,7 +6702,7 @@
       </c>
       <c r="H275" s="5"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="7">
         <v>45435</v>
       </c>
@@ -6641,7 +6726,7 @@
       </c>
       <c r="H276" s="5"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="7">
         <v>45484</v>
       </c>
@@ -6662,7 +6747,7 @@
       </c>
       <c r="H277" s="5"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="7">
         <v>45526</v>
       </c>
@@ -6686,7 +6771,7 @@
       </c>
       <c r="H278" s="5"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="7">
         <v>45576</v>
       </c>
@@ -6710,7 +6795,7 @@
       </c>
       <c r="H279" s="5"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="7">
         <v>45624</v>
       </c>
@@ -6734,7 +6819,7 @@
       </c>
       <c r="H280" s="5"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="7">
         <v>45673</v>
       </c>
@@ -6758,7 +6843,7 @@
       </c>
       <c r="H281" s="5"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="7">
         <v>45713</v>
       </c>
@@ -6782,7 +6867,7 @@
       </c>
       <c r="H282" s="5"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="7">
         <v>45764</v>
       </c>
@@ -6806,7 +6891,7 @@
       </c>
       <c r="H283" s="5"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="7">
         <v>45806</v>
       </c>
@@ -6830,7 +6915,7 @@
       </c>
       <c r="H284" s="5"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="7">
         <v>45848</v>
       </c>
@@ -6854,7 +6939,7 @@
       </c>
       <c r="H285" s="5"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="7">
         <v>45897</v>
       </c>
@@ -6878,7 +6963,7 @@
       </c>
       <c r="H286" s="5"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="7">
         <v>45953</v>
       </c>
@@ -6902,7 +6987,7 @@
       </c>
       <c r="H287" s="5"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="7">
         <v>45988</v>
       </c>
@@ -6926,7 +7011,7 @@
       </c>
       <c r="H288" s="5"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="7">
         <v>46037</v>
       </c>
@@ -6950,7 +7035,7 @@
       </c>
       <c r="H289" s="5"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="7">
         <v>46079</v>
       </c>
@@ -6974,7 +7059,7 @@
       </c>
       <c r="H290" s="5"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="7">
         <v>46122</v>
       </c>
@@ -6997,7 +7082,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="7">
         <v>46170</v>
       </c>
@@ -7020,7 +7105,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="7">
         <v>46219</v>
       </c>
@@ -7043,7 +7128,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="7">
         <v>46261</v>
       </c>
@@ -7056,8 +7141,17 @@
       <c r="D294" s="9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E294" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="F294" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="G294" s="10">
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="7">
         <v>46317</v>
       </c>
@@ -7071,7 +7165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="7">
         <v>46352</v>
       </c>
@@ -7092,4 +7186,71 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CC5C4A-BF6B-4649-B1EC-897CDF31D19C}">
+  <dimension ref="B2:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="8.83203125" style="13"/>
+    <col min="3" max="3" width="12.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="82.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="14">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>